--- a/excel_files/1.2.2.xlsx
+++ b/excel_files/1.2.2.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D093DA83-1626-4241-A9D8-E199AB22B536}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13650" windowHeight="8070"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="3" r:id="rId1"/>
@@ -244,7 +245,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
@@ -434,12 +435,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -448,9 +449,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -460,42 +458,35 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -504,37 +495,27 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
@@ -547,13 +528,27 @@
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 2" xfId="1"/>
-    <cellStyle name="Обычный 6" xfId="2"/>
+    <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Обычный 6" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -569,9 +564,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -609,9 +604,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -646,7 +641,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -681,7 +676,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -854,8 +849,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N88"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:L36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="35" style="3" customWidth="1"/>
@@ -864,140 +859,135 @@
     <col min="11" max="11" width="8.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="K3" s="15"/>
-      <c r="L3" s="15"/>
-      <c r="M3" s="15"/>
-      <c r="N3" s="15"/>
-    </row>
-    <row r="4" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L3" s="34"/>
+    </row>
+    <row r="4" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4" s="7">
         <v>2016</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="7">
         <v>2017</v>
       </c>
-      <c r="F4" s="8">
+      <c r="F4" s="7">
         <v>2018</v>
       </c>
-      <c r="G4" s="8">
+      <c r="G4" s="7">
         <v>2019</v>
       </c>
-      <c r="H4" s="8">
+      <c r="H4" s="7">
         <v>2020</v>
       </c>
-      <c r="I4" s="8">
+      <c r="I4" s="7">
         <v>2021</v>
       </c>
-      <c r="J4" s="8">
+      <c r="J4" s="7">
         <v>2022</v>
       </c>
-      <c r="K4" s="8">
+      <c r="K4" s="7">
         <v>2023</v>
       </c>
-      <c r="L4" s="15"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="15"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="26" t="s">
+      <c r="L4" s="35">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="26" t="s">
+      <c r="C5" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="12">
         <v>50.2</v>
       </c>
-      <c r="E5" s="14">
+      <c r="E5" s="12">
         <v>50.5</v>
       </c>
-      <c r="F5" s="14">
+      <c r="F5" s="12">
         <v>45.8</v>
       </c>
-      <c r="G5" s="14">
+      <c r="G5" s="12">
         <v>42.3</v>
       </c>
-      <c r="H5" s="14">
+      <c r="H5" s="12">
         <v>42.2</v>
       </c>
-      <c r="I5" s="14">
+      <c r="I5" s="12">
         <v>48.5</v>
       </c>
-      <c r="J5" s="40">
+      <c r="J5" s="30">
         <v>47.4</v>
       </c>
-      <c r="K5" s="40">
+      <c r="K5" s="30">
         <v>43.6</v>
       </c>
-      <c r="L5" s="15"/>
-      <c r="M5" s="15"/>
-      <c r="N5" s="15"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="37" t="s">
+      <c r="L5" s="39">
+        <v>38.463125318612718</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="B6" s="38" t="s">
+      <c r="B6" s="28" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="37" t="s">
+      <c r="C6" s="24" t="s">
         <v>46</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
-      <c r="F6" s="33"/>
-      <c r="G6" s="33"/>
-      <c r="H6" s="33"/>
-      <c r="I6" s="33"/>
-      <c r="J6" s="41"/>
-      <c r="K6" s="41"/>
-      <c r="L6" s="15"/>
-      <c r="M6" s="15"/>
-      <c r="N6" s="15"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="17" t="s">
+      <c r="F6" s="25"/>
+      <c r="G6" s="25"/>
+      <c r="H6" s="25"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="31"/>
+      <c r="K6" s="31"/>
+      <c r="L6" s="37"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="28" t="s">
+      <c r="B7" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="16" t="s">
         <v>13</v>
       </c>
       <c r="D7" s="2">
@@ -1006,36 +996,36 @@
       <c r="E7" s="2">
         <v>50.3</v>
       </c>
-      <c r="F7" s="33">
+      <c r="F7" s="25">
         <v>45.8</v>
       </c>
-      <c r="G7" s="33">
+      <c r="G7" s="25">
         <v>42.7</v>
       </c>
-      <c r="H7" s="33">
+      <c r="H7" s="25">
         <v>42.5</v>
       </c>
-      <c r="I7" s="33">
+      <c r="I7" s="25">
         <v>48.8</v>
       </c>
-      <c r="J7" s="41">
+      <c r="J7" s="31">
         <v>47.9</v>
       </c>
-      <c r="K7" s="41">
+      <c r="K7" s="31">
         <v>43.5</v>
       </c>
-      <c r="L7" s="15"/>
-      <c r="M7" s="15"/>
-      <c r="N7" s="15"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="17" t="s">
+      <c r="L7" s="36">
+        <v>38.517908977624963</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="28" t="s">
+      <c r="B8" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="16" t="s">
         <v>15</v>
       </c>
       <c r="D8" s="2">
@@ -1044,58 +1034,56 @@
       <c r="E8" s="2">
         <v>50.6</v>
       </c>
-      <c r="F8" s="33">
+      <c r="F8" s="25">
         <v>45.9</v>
       </c>
-      <c r="G8" s="33">
+      <c r="G8" s="25">
         <v>41.9</v>
       </c>
-      <c r="H8" s="36">
+      <c r="H8" s="27">
         <v>42</v>
       </c>
-      <c r="I8" s="36">
+      <c r="I8" s="27">
         <v>48.2</v>
       </c>
-      <c r="J8" s="42">
+      <c r="J8" s="32">
         <v>46.9</v>
       </c>
-      <c r="K8" s="42">
+      <c r="K8" s="32">
         <v>43.6</v>
       </c>
-      <c r="L8" s="15"/>
-      <c r="M8" s="15"/>
-      <c r="N8" s="15"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="37" t="s">
+      <c r="L8" s="36">
+        <v>38.413730992512619</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="B9" s="38" t="s">
+      <c r="B9" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="38" t="s">
+      <c r="C9" s="28" t="s">
         <v>45</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
-      <c r="F9" s="33"/>
-      <c r="G9" s="33"/>
-      <c r="H9" s="33"/>
-      <c r="I9" s="33"/>
-      <c r="J9" s="41"/>
-      <c r="K9" s="41"/>
-      <c r="L9" s="15"/>
-      <c r="M9" s="15"/>
-      <c r="N9" s="15"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="18" t="s">
+      <c r="F9" s="25"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="25"/>
+      <c r="I9" s="25"/>
+      <c r="J9" s="31"/>
+      <c r="K9" s="31"/>
+      <c r="L9" s="36"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="B10" s="28" t="s">
+      <c r="B10" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="C10" s="28" t="s">
+      <c r="C10" s="14" t="s">
         <v>47</v>
       </c>
       <c r="D10" s="2">
@@ -1104,36 +1092,36 @@
       <c r="E10" s="2">
         <v>60</v>
       </c>
-      <c r="F10" s="36">
+      <c r="F10" s="27">
         <v>56</v>
       </c>
-      <c r="G10" s="36">
+      <c r="G10" s="27">
         <v>52</v>
       </c>
-      <c r="H10" s="36">
+      <c r="H10" s="27">
         <v>50.9</v>
       </c>
-      <c r="I10" s="36">
+      <c r="I10" s="27">
         <v>58.2</v>
       </c>
-      <c r="J10" s="42">
+      <c r="J10" s="32">
         <v>56.8</v>
       </c>
-      <c r="K10" s="42">
+      <c r="K10" s="32">
         <v>52.6</v>
       </c>
-      <c r="L10" s="15"/>
-      <c r="M10" s="15"/>
-      <c r="N10" s="15"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="25" t="s">
+      <c r="L10" s="36">
+        <v>48.510457087342637</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="B11" s="28" t="s">
+      <c r="B11" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="28" t="s">
+      <c r="C11" s="14" t="s">
         <v>48</v>
       </c>
       <c r="D11" s="2">
@@ -1142,737 +1130,549 @@
       <c r="E11" s="2">
         <v>44.1</v>
       </c>
-      <c r="F11" s="33">
+      <c r="F11" s="25">
         <v>39.299999999999997</v>
       </c>
-      <c r="G11" s="33">
+      <c r="G11" s="25">
         <v>35.9</v>
       </c>
-      <c r="H11" s="33">
+      <c r="H11" s="25">
         <v>36.9</v>
       </c>
-      <c r="I11" s="33">
+      <c r="I11" s="25">
         <v>42.4</v>
       </c>
-      <c r="J11" s="41">
+      <c r="J11" s="31">
         <v>41.4</v>
       </c>
-      <c r="K11" s="41">
+      <c r="K11" s="31">
         <v>38.200000000000003</v>
       </c>
-      <c r="L11" s="15"/>
-      <c r="M11" s="15"/>
-      <c r="N11" s="15"/>
-    </row>
-    <row r="12" spans="1:14" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="25" t="s">
+      <c r="L11" s="36">
+        <v>32.186861818718796</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="B12" s="28" t="s">
+      <c r="B12" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="28" t="s">
+      <c r="C12" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="D12" s="25">
+      <c r="D12" s="15">
         <v>49.2</v>
       </c>
-      <c r="E12" s="29">
+      <c r="E12" s="22">
         <v>46.4</v>
       </c>
-      <c r="F12" s="33">
+      <c r="F12" s="25">
         <v>38.6</v>
       </c>
-      <c r="G12" s="33">
+      <c r="G12" s="25">
         <v>37</v>
       </c>
-      <c r="H12" s="33">
+      <c r="H12" s="25">
         <v>34.799999999999997</v>
       </c>
-      <c r="I12" s="33">
+      <c r="I12" s="25">
         <v>40.700000000000003</v>
       </c>
-      <c r="J12" s="42">
+      <c r="J12" s="32">
         <v>39</v>
       </c>
-      <c r="K12" s="42">
+      <c r="K12" s="32">
         <v>33.9</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="16" t="s">
+      <c r="L12" s="36">
+        <v>30.026662552193532</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="38" t="s">
+      <c r="B13" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="39" t="s">
+      <c r="C13" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="D13" s="9"/>
+      <c r="D13" s="8"/>
       <c r="E13" s="2"/>
-      <c r="F13" s="33"/>
-      <c r="G13" s="33"/>
-      <c r="H13" s="33"/>
-      <c r="I13" s="33"/>
-      <c r="J13" s="41"/>
-      <c r="K13" s="41"/>
-      <c r="L13" s="15"/>
-      <c r="M13" s="15"/>
-      <c r="N13" s="15"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="17" t="s">
+      <c r="F13" s="25"/>
+      <c r="G13" s="25"/>
+      <c r="H13" s="25"/>
+      <c r="I13" s="25"/>
+      <c r="J13" s="31"/>
+      <c r="K13" s="31"/>
+      <c r="L13" s="36"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="B14" s="28" t="s">
+      <c r="B14" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="C14" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="D14" s="9">
+      <c r="D14" s="8">
         <v>36.9</v>
       </c>
       <c r="E14" s="2">
         <v>38.700000000000003</v>
       </c>
-      <c r="F14" s="33">
+      <c r="F14" s="25">
         <v>33.799999999999997</v>
       </c>
-      <c r="G14" s="33">
+      <c r="G14" s="25">
         <v>31.1</v>
       </c>
-      <c r="H14" s="33">
+      <c r="H14" s="25">
         <v>30.7</v>
       </c>
-      <c r="I14" s="33">
+      <c r="I14" s="25">
         <v>41.5</v>
       </c>
-      <c r="J14" s="41">
+      <c r="J14" s="31">
         <v>39.5</v>
       </c>
-      <c r="K14" s="41">
+      <c r="K14" s="31">
         <v>36.799999999999997</v>
       </c>
-      <c r="L14" s="15"/>
-      <c r="M14" s="15"/>
-      <c r="N14" s="15"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="17" t="s">
+      <c r="L14" s="36">
+        <v>28.329009354102872</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="B15" s="28" t="s">
+      <c r="B15" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="19" t="s">
+      <c r="C15" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="D15" s="9">
+      <c r="D15" s="8">
         <v>57.4</v>
       </c>
       <c r="E15" s="2">
         <v>56.8</v>
       </c>
-      <c r="F15" s="33">
+      <c r="F15" s="25">
         <v>52.4</v>
       </c>
-      <c r="G15" s="33">
+      <c r="G15" s="25">
         <v>48.5</v>
       </c>
-      <c r="H15" s="33">
+      <c r="H15" s="25">
         <v>48.8</v>
       </c>
-      <c r="I15" s="33">
+      <c r="I15" s="25">
         <v>52.6</v>
       </c>
-      <c r="J15" s="41">
+      <c r="J15" s="31">
         <v>51.9</v>
       </c>
-      <c r="K15" s="41">
+      <c r="K15" s="31">
         <v>47.4</v>
       </c>
-      <c r="L15" s="15"/>
-      <c r="M15" s="15"/>
-      <c r="N15" s="15"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="16" t="s">
+      <c r="L15" s="36">
+        <v>45.99791956498381</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="38" t="s">
+      <c r="B16" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="C16" s="37" t="s">
+      <c r="C16" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="D16" s="9"/>
+      <c r="D16" s="8"/>
       <c r="E16" s="2"/>
-      <c r="F16" s="33"/>
-      <c r="G16" s="33"/>
-      <c r="H16" s="33"/>
-      <c r="I16" s="33"/>
-      <c r="J16" s="41"/>
-      <c r="K16" s="41"/>
-      <c r="L16" s="15"/>
-      <c r="M16" s="15"/>
-      <c r="N16" s="15"/>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="20" t="s">
+      <c r="F16" s="25"/>
+      <c r="G16" s="25"/>
+      <c r="H16" s="25"/>
+      <c r="I16" s="25"/>
+      <c r="J16" s="31"/>
+      <c r="K16" s="31"/>
+      <c r="L16" s="36"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="B17" s="28" t="s">
+      <c r="B17" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="19" t="s">
+      <c r="C17" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="D17" s="9">
+      <c r="D17" s="8">
         <v>64.900000000000006</v>
       </c>
       <c r="E17" s="2">
         <v>66</v>
       </c>
-      <c r="F17" s="33">
+      <c r="F17" s="25">
         <v>64.8</v>
       </c>
-      <c r="G17" s="33">
+      <c r="G17" s="25">
         <v>63.5</v>
       </c>
-      <c r="H17" s="33">
+      <c r="H17" s="25">
         <v>61.1</v>
       </c>
-      <c r="I17" s="33">
+      <c r="I17" s="25">
         <v>67.099999999999994</v>
       </c>
-      <c r="J17" s="41">
+      <c r="J17" s="31">
         <v>69.900000000000006</v>
       </c>
-      <c r="K17" s="41">
+      <c r="K17" s="31">
         <v>69.3</v>
       </c>
-      <c r="L17" s="15"/>
-      <c r="M17" s="15"/>
-      <c r="N17" s="15"/>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="20" t="s">
+      <c r="L17" s="36">
+        <v>61.806104269799512</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="B18" s="28" t="s">
+      <c r="B18" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="21" t="s">
+      <c r="C18" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="D18" s="9">
+      <c r="D18" s="8">
         <v>59.6</v>
       </c>
       <c r="E18" s="2">
         <v>61.5</v>
       </c>
-      <c r="F18" s="33">
+      <c r="F18" s="25">
         <v>53.8</v>
       </c>
-      <c r="G18" s="33">
+      <c r="G18" s="25">
         <v>50.4</v>
       </c>
-      <c r="H18" s="33">
+      <c r="H18" s="25">
         <v>56.7</v>
       </c>
-      <c r="I18" s="33">
+      <c r="I18" s="25">
         <v>62</v>
       </c>
-      <c r="J18" s="42">
+      <c r="J18" s="32">
         <v>61</v>
       </c>
-      <c r="K18" s="42">
+      <c r="K18" s="32">
         <v>54.9</v>
       </c>
-      <c r="L18" s="15"/>
-      <c r="M18" s="15"/>
-      <c r="N18" s="15"/>
-    </row>
-    <row r="19" spans="1:14" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="20" t="s">
+      <c r="L18" s="36">
+        <v>47.244867056307314</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="B19" s="28" t="s">
+      <c r="B19" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="21" t="s">
+      <c r="C19" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="D19" s="25">
+      <c r="D19" s="15">
         <v>45.2</v>
       </c>
       <c r="E19" s="2">
         <v>47</v>
       </c>
-      <c r="F19" s="33">
+      <c r="F19" s="25">
         <v>42.7</v>
       </c>
-      <c r="G19" s="33">
+      <c r="G19" s="25">
         <v>46.3</v>
       </c>
-      <c r="H19" s="33">
+      <c r="H19" s="25">
         <v>41.6</v>
       </c>
-      <c r="I19" s="33">
+      <c r="I19" s="25">
         <v>46.9</v>
       </c>
-      <c r="J19" s="41">
+      <c r="J19" s="31">
         <v>42.5</v>
       </c>
-      <c r="K19" s="41">
+      <c r="K19" s="31">
         <v>45.4</v>
       </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="20" t="s">
+      <c r="L19" s="36">
+        <v>41.573379644241008</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="B20" s="28" t="s">
+      <c r="B20" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C20" s="21" t="s">
+      <c r="C20" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="D20" s="9">
+      <c r="D20" s="8">
         <v>58.3</v>
       </c>
       <c r="E20" s="2">
         <v>50</v>
       </c>
-      <c r="F20" s="33">
+      <c r="F20" s="25">
         <v>48.5</v>
       </c>
-      <c r="G20" s="33">
+      <c r="G20" s="25">
         <v>47.8</v>
       </c>
-      <c r="H20" s="36">
+      <c r="H20" s="27">
         <v>49</v>
       </c>
-      <c r="I20" s="36">
+      <c r="I20" s="27">
         <v>55.8</v>
       </c>
-      <c r="J20" s="42">
+      <c r="J20" s="32">
         <v>54</v>
       </c>
-      <c r="K20" s="42">
+      <c r="K20" s="32">
         <v>49.3</v>
       </c>
-      <c r="L20" s="35"/>
-      <c r="M20" s="15"/>
-      <c r="N20" s="15"/>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="20" t="s">
+      <c r="L20" s="36">
+        <v>47.507469737403405</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="B21" s="28" t="s">
+      <c r="B21" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="21" t="s">
+      <c r="C21" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="D21" s="9">
+      <c r="D21" s="8">
         <v>57.5</v>
       </c>
       <c r="E21" s="2">
         <v>52.1</v>
       </c>
-      <c r="F21" s="33">
+      <c r="F21" s="25">
         <v>58.5</v>
       </c>
-      <c r="G21" s="33">
+      <c r="G21" s="25">
         <v>45.8</v>
       </c>
-      <c r="H21" s="33">
+      <c r="H21" s="25">
         <v>43.5</v>
       </c>
-      <c r="I21" s="33">
+      <c r="I21" s="25">
         <v>42.7</v>
       </c>
-      <c r="J21" s="41">
+      <c r="J21" s="31">
         <v>42.5</v>
       </c>
-      <c r="K21" s="41">
+      <c r="K21" s="31">
         <v>37.1</v>
       </c>
-      <c r="L21" s="35"/>
-      <c r="M21" s="15"/>
-      <c r="N21" s="15"/>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="20" t="s">
+      <c r="L21" s="36">
+        <v>40.569902686076773</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="B22" s="28" t="s">
+      <c r="B22" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="C22" s="21" t="s">
+      <c r="C22" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="D22" s="9">
+      <c r="D22" s="8">
         <v>49.8</v>
       </c>
       <c r="E22" s="2">
         <v>39.799999999999997</v>
       </c>
-      <c r="F22" s="36">
+      <c r="F22" s="27">
         <v>43</v>
       </c>
-      <c r="G22" s="36">
+      <c r="G22" s="27">
         <v>40.200000000000003</v>
       </c>
-      <c r="H22" s="36">
+      <c r="H22" s="27">
         <v>33.9</v>
       </c>
-      <c r="I22" s="36">
+      <c r="I22" s="27">
         <v>48.3</v>
       </c>
-      <c r="J22" s="42">
+      <c r="J22" s="32">
         <v>45.8</v>
       </c>
-      <c r="K22" s="42">
+      <c r="K22" s="32">
         <v>41.1</v>
       </c>
-      <c r="L22" s="35"/>
-      <c r="M22" s="15"/>
-      <c r="N22" s="15"/>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="20" t="s">
+      <c r="L22" s="36">
+        <v>33.785512484806503</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="B23" s="28" t="s">
+      <c r="B23" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="C23" s="21" t="s">
+      <c r="C23" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="D23" s="9">
+      <c r="D23" s="8">
         <v>45.4</v>
       </c>
-      <c r="E23" s="33">
+      <c r="E23" s="25">
         <v>48.7</v>
       </c>
-      <c r="F23" s="36">
+      <c r="F23" s="27">
         <v>28</v>
       </c>
-      <c r="G23" s="36">
+      <c r="G23" s="27">
         <v>31.7</v>
       </c>
-      <c r="H23" s="36">
+      <c r="H23" s="27">
         <v>34.6</v>
       </c>
-      <c r="I23" s="36">
+      <c r="I23" s="27">
         <v>39.700000000000003</v>
       </c>
-      <c r="J23" s="42">
+      <c r="J23" s="32">
         <v>38.1</v>
       </c>
-      <c r="K23" s="42">
+      <c r="K23" s="32">
         <v>35.700000000000003</v>
       </c>
-      <c r="L23" s="35"/>
-      <c r="M23" s="15"/>
-      <c r="N23" s="15"/>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="22" t="s">
+      <c r="L23" s="36">
+        <v>31.015036030236885</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="B24" s="30" t="s">
+      <c r="B24" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="C24" s="21" t="s">
+      <c r="C24" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="D24" s="9">
+      <c r="D24" s="8">
         <v>26.8</v>
       </c>
-      <c r="E24" s="33">
+      <c r="E24" s="25">
         <v>29.9</v>
       </c>
-      <c r="F24" s="33">
+      <c r="F24" s="25">
         <v>25.4</v>
       </c>
-      <c r="G24" s="33">
+      <c r="G24" s="25">
         <v>22.2</v>
       </c>
-      <c r="H24" s="33">
+      <c r="H24" s="25">
         <v>23.6</v>
       </c>
-      <c r="I24" s="33">
+      <c r="I24" s="25">
         <v>38.1</v>
       </c>
-      <c r="J24" s="41">
+      <c r="J24" s="31">
         <v>38.9</v>
       </c>
-      <c r="K24" s="41">
+      <c r="K24" s="31">
         <v>36.799999999999997</v>
       </c>
-      <c r="L24" s="35"/>
-      <c r="M24" s="15"/>
-      <c r="N24" s="15"/>
-    </row>
-    <row r="25" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="31" t="s">
+      <c r="L24" s="36">
+        <v>28.197480781735926</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="B25" s="31" t="s">
+      <c r="B25" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="C25" s="31" t="s">
+      <c r="C25" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="D25" s="10">
+      <c r="D25" s="9">
         <v>47.3</v>
       </c>
-      <c r="E25" s="34">
+      <c r="E25" s="26">
         <v>58.6</v>
       </c>
-      <c r="F25" s="34">
+      <c r="F25" s="26">
         <v>51.3</v>
       </c>
-      <c r="G25" s="34">
+      <c r="G25" s="26">
         <v>45.9</v>
       </c>
-      <c r="H25" s="34">
+      <c r="H25" s="26">
         <v>35.9</v>
       </c>
-      <c r="I25" s="34">
+      <c r="I25" s="26">
         <v>44.7</v>
       </c>
-      <c r="J25" s="43">
+      <c r="J25" s="33">
         <v>38.700000000000003</v>
       </c>
-      <c r="K25" s="43">
+      <c r="K25" s="33">
         <v>26</v>
       </c>
-      <c r="L25" s="35"/>
-      <c r="M25" s="15"/>
-      <c r="N25" s="15"/>
-    </row>
-    <row r="26" spans="1:14" ht="36.75" x14ac:dyDescent="0.25">
-      <c r="A26" s="23" t="s">
+      <c r="L25" s="38">
+        <v>14.080930116484137</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="36.75" x14ac:dyDescent="0.25">
+      <c r="A26" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="B26" s="24" t="s">
+      <c r="B26" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="C26" s="23" t="s">
+      <c r="C26" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="D26" s="29"/>
-      <c r="E26" s="29"/>
-      <c r="F26" s="27"/>
-      <c r="K26" s="15"/>
-      <c r="L26" s="15"/>
-      <c r="M26" s="15"/>
-      <c r="N26" s="15"/>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="K27" s="15"/>
-      <c r="L27" s="15"/>
-      <c r="M27" s="15"/>
-      <c r="N27" s="15"/>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="K28" s="15"/>
-      <c r="L28" s="15"/>
-      <c r="M28" s="15"/>
-      <c r="N28" s="15"/>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="K29" s="15"/>
-      <c r="L29" s="15"/>
-      <c r="M29" s="15"/>
-      <c r="N29" s="15"/>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="K30" s="15"/>
-      <c r="L30" s="15"/>
-      <c r="M30" s="15"/>
-      <c r="N30" s="15"/>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="K31" s="15"/>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="K32" s="15"/>
+      <c r="D26" s="22"/>
+      <c r="E26" s="22"/>
+      <c r="F26" s="22"/>
     </row>
     <row r="33" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K33" s="32"/>
+      <c r="K33" s="24"/>
     </row>
     <row r="34" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K34" s="25"/>
+      <c r="K34" s="15"/>
     </row>
     <row r="35" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K35" s="25"/>
+      <c r="K35" s="15"/>
     </row>
     <row r="36" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K36" s="25"/>
-    </row>
-    <row r="37" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K37" s="15"/>
-    </row>
-    <row r="38" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K38" s="15"/>
-    </row>
-    <row r="39" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K39" s="15"/>
-    </row>
-    <row r="40" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K40" s="15"/>
-    </row>
-    <row r="41" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K41" s="15"/>
-    </row>
-    <row r="42" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K42" s="15"/>
-    </row>
-    <row r="43" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K43" s="15"/>
-    </row>
-    <row r="44" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K44" s="15"/>
-    </row>
-    <row r="45" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K45" s="15"/>
-    </row>
-    <row r="46" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K46" s="15"/>
-    </row>
-    <row r="47" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K47" s="15"/>
-    </row>
-    <row r="48" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K48" s="15"/>
-    </row>
-    <row r="49" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K49" s="15"/>
-    </row>
-    <row r="50" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K50" s="15"/>
-    </row>
-    <row r="51" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K51" s="15"/>
-    </row>
-    <row r="52" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K52" s="15"/>
-    </row>
-    <row r="53" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K53" s="15"/>
-    </row>
-    <row r="54" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K54" s="15"/>
-    </row>
-    <row r="55" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K55" s="15"/>
-    </row>
-    <row r="56" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K56" s="15"/>
-    </row>
-    <row r="57" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K57" s="15"/>
-    </row>
-    <row r="58" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K58" s="15"/>
-    </row>
-    <row r="59" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K59" s="15"/>
-    </row>
-    <row r="60" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K60" s="15"/>
-    </row>
-    <row r="61" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K61" s="15"/>
-    </row>
-    <row r="62" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K62" s="15"/>
-    </row>
-    <row r="63" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K63" s="15"/>
-    </row>
-    <row r="64" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K64" s="15"/>
-    </row>
-    <row r="65" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K65" s="15"/>
-    </row>
-    <row r="66" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K66" s="15"/>
-    </row>
-    <row r="67" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K67" s="15"/>
-    </row>
-    <row r="68" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K68" s="15"/>
-    </row>
-    <row r="69" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K69" s="15"/>
-    </row>
-    <row r="70" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K70" s="15"/>
-    </row>
-    <row r="71" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K71" s="15"/>
-    </row>
-    <row r="72" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K72" s="15"/>
-    </row>
-    <row r="73" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K73" s="15"/>
-    </row>
-    <row r="74" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K74" s="15"/>
-    </row>
-    <row r="75" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K75" s="15"/>
-    </row>
-    <row r="76" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K76" s="15"/>
-    </row>
-    <row r="77" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K77" s="15"/>
-    </row>
-    <row r="78" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K78" s="15"/>
-    </row>
-    <row r="79" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K79" s="15"/>
-    </row>
-    <row r="80" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K80" s="15"/>
-    </row>
-    <row r="81" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K81" s="15"/>
-    </row>
-    <row r="82" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K82" s="15"/>
-    </row>
-    <row r="83" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K83" s="15"/>
-    </row>
-    <row r="84" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K84" s="15"/>
-    </row>
-    <row r="85" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K85" s="15"/>
-    </row>
-    <row r="86" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K86" s="15"/>
-    </row>
-    <row r="87" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K87" s="15"/>
-    </row>
-    <row r="88" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K88" s="15"/>
+      <c r="K36" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
